--- a/News_Dashboard/data/raw_news_database_Mondee.xlsx
+++ b/News_Dashboard/data/raw_news_database_Mondee.xlsx
@@ -2846,17 +2846,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Develop a dedicated API integration layer that allows travel advisors to pull MONDEE’s itinerary optimization data directly into Expedia TAAP, positioning MONDEE as the preferred data partner for US travel advisors.</t>
+          <t>Develop a white‑label travel engine for US brands, mirroring Priceline Partner Network, to capture the white‑label market and compete with Booking Holdings.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Launch a white‑label travel engine tailored for US brands, mirroring Priceline Partner Network’s model, and target mid‑market travel agencies seeking a customizable booking platform.</t>
+          <t>Launch a US‑focused travel‑advisor platform with behind‑the‑scenes tools and back‑office APIs, directly competing with Expedia TAAP’s new engine.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Partner with Vancouver’s tourism authority to create a pedestrian‑centric mobile guide app that highlights the new car‑free Granville Street, positioning MONDEE as the go‑to tech partner for sustainable urban travel experiences.</t>
+          <t>Partner with Vancouver tourism authorities to create a “Granville Green Travel” package, promoting the car‑free zone to eco‑conscious travelers and showcasing MONDEE’s sustainable travel expertise.</t>
         </is>
       </c>
     </row>
@@ -2900,17 +2900,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Launch a US‑focused travel advisor platform that mirrors Expedia TAAP, integrating a robust back‑office API and real‑time inventory tools to give advisors seamless booking and reporting capabilities.</t>
+          <t>Launch a dedicated back‑office API suite for US travel advisors, mirroring Expedia TAAP’s functionality, and offer a pilot program to the top 20 advisors to secure early adopters.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Introduce a white‑label travel engine partnership program similar to Priceline Partner Network, allowing agencies to brand our booking engine while we handle inventory, pricing, and compliance.</t>
+          <t>Develop a white‑label travel engine that integrates seamlessly with partner platforms, positioning MONDEE as a flexible alternative to Priceline Partner Network, and initiate outreach to mid‑market OTA partners within the next 30 days.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Deploy advanced data‑driven analytics dashboards for advisors, offering predictive pricing, demand forecasting, and personalized travel recommendations that differentiate us from generic competitor APIs.</t>
+          <t>Create a co‑marketing partnership with a leading US travel advisory firm to showcase MONDEE’s real‑time inventory and dynamic pricing, leveraging the momentum from Expedia TAAP’s launch to capture advisor market share.</t>
         </is>
       </c>
     </row>
@@ -2927,17 +2927,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Launch a dedicated back‑office API suite for travel advisors that includes real‑time booking reference tools and automated commission tracking, directly addressing the gap left by Expedia TAAP’s recent rollout; pilot this with a select group of high‑volume agencies within 90 days.</t>
+          <t>Develop a dedicated back‑office API suite for travel advisors, mirroring Expedia TAAP’s new tools, and launch a pilot with 10 high‑volume agencies within 90 days to secure early adopters and gather feedback for rapid iteration. This will position MONDEE as the preferred partner for agencies seeking streamlined operations and differentiate us from competitors.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Develop a curated “Granville Street Experience” package on MONDEE that bundles accommodation, dining, and walking tours around Vancouver’s new pedestrian zone, and promote it through local tourism partners to capture the influx of visitors highlighted by Downtown Travel’s expansion.</t>
+          <t>Leverage the Priceline Partner Network’s white‑label engine by integrating it into MONDEE’s platform as a plug‑in, offering clients a seamless, branded booking experience while retaining revenue share, and roll out a marketing campaign targeting mid‑market travel agencies within 60 days.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Negotiate a white‑label integration with Priceline Partner Network’s engine to offer MONDEE’s travel solutions under partner brands, leveraging their existing distribution while differentiating with our AI‑driven itinerary personalization; target a pilot launch in the next fiscal quarter.</t>
+          <t>Capitalize on Vancouver’s new pedestrian zone by creating a localized travel package that includes exclusive access to Granville Street events, partnering with local businesses, and promoting it through MONDEE’s mobile app and social channels within 45 days to capture the growing urban tourism market.</t>
         </is>
       </c>
     </row>
@@ -2981,17 +2981,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Launch a dedicated back‑office API and suite of tools for travel advisors, mirroring Expedia TAAP’s recent rollout, and pilot it with a select group of high‑volume agencies to validate integration ease and operational efficiency.</t>
+          <t>Launch a back‑office API suite for travel advisors that mirrors Expedia TAAP’s new tools, enabling agencies to manage bookings, references, and reporting directly from MONDEE’s platform.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Secure a partnership with a leading travel agency network to embed MONDEE’s white‑label travel engine, positioning it as a direct competitor to Priceline Partner Network’s quiet engine, and promote joint marketing to agencies.</t>
+          <t>Introduce a tiered rewards program for agencies that book through MONDEE, matching or exceeding Expedia TAAP’s rewards to incentivize partner loyalty.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Introduce a tiered rewards program for advisors that offers commission boosts and exclusive benefits, directly countering Expedia TAAP’s rewards launch, and roll it out through a targeted email campaign to existing advisor partners.</t>
+          <t>Partner with Priceline Partner Network to embed MONDEE’s AI‑driven itinerary optimization into their white‑label engine, creating a differentiated, value‑added offering that counters Expedia’s agency focus.</t>
         </is>
       </c>
     </row>

--- a/News_Dashboard/data/raw_news_database_Mondee.xlsx
+++ b/News_Dashboard/data/raw_news_database_Mondee.xlsx
@@ -2846,17 +2846,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Develop a white‑label travel engine for US brands, mirroring Priceline Partner Network, to capture the white‑label market and compete with Booking Holdings.</t>
+          <t>Develop a back‑office API and tools tailored for US travel advisors, mirroring Expedia TAAP, and launch a pilot with the top 10 agencies to secure early adoption.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Launch a US‑focused travel‑advisor platform with behind‑the‑scenes tools and back‑office APIs, directly competing with Expedia TAAP’s new engine.</t>
+          <t>Create a white‑label travel engine for US brands, offering a revenue‑share model to compete with Priceline Partner Network’s white‑label solution, and target 5 major brands for beta testing.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Partner with Vancouver tourism authorities to create a “Granville Green Travel” package, promoting the car‑free zone to eco‑conscious travelers and showcasing MONDEE’s sustainable travel expertise.</t>
+          <t>Partner with Vancouver’s tourism board to build a digital guide and booking integration for the new car‑free Granville Street zone, positioning MONDEE as the preferred tech partner for the expanded pedestrian experience.</t>
         </is>
       </c>
     </row>
@@ -2900,17 +2900,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Launch a dedicated back‑office API suite for US travel advisors, mirroring Expedia TAAP’s functionality, and offer a pilot program to the top 20 advisors to secure early adopters.</t>
+          <t>Launch a proprietary TAAP‑style platform for US travel advisors, integrating a back‑office API and tools to streamline booking workflows and position MONDEE as the go‑to advisor solution.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Develop a white‑label travel engine that integrates seamlessly with partner platforms, positioning MONDEE as a flexible alternative to Priceline Partner Network, and initiate outreach to mid‑market OTA partners within the next 30 days.</t>
+          <t>Develop a white‑label travel engine that partners can embed in their own sites, mirroring Priceline Partner Network’s model, to expand MONDEE’s distribution and revenue streams.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Create a co‑marketing partnership with a leading US travel advisory firm to showcase MONDEE’s real‑time inventory and dynamic pricing, leveraging the momentum from Expedia TAAP’s launch to capture advisor market share.</t>
+          <t>Conduct a rapid market analysis of US travel advisor pain points revealed by Expedia’s TAAP rollout, then develop a targeted feature set (e.g., real‑time inventory, commission management) to outpace competitors in advisor adoption.</t>
         </is>
       </c>
     </row>
@@ -2927,17 +2927,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Develop a dedicated back‑office API suite for travel advisors, mirroring Expedia TAAP’s new tools, and launch a pilot with 10 high‑volume agencies within 90 days to secure early adopters and gather feedback for rapid iteration. This will position MONDEE as the preferred partner for agencies seeking streamlined operations and differentiate us from competitors.</t>
+          <t>Launch a dedicated back‑office API suite for travel advisors that mirrors Expedia TAAP’s new tools, enabling agencies to manage bookings, references, and reporting directly within MONDEE’s platform; begin beta testing with 5 key agency partners within 90 days. This will position MONDEE as a direct alternative to TAAP and retain agency loyalty.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Leverage the Priceline Partner Network’s white‑label engine by integrating it into MONDEE’s platform as a plug‑in, offering clients a seamless, branded booking experience while retaining revenue share, and roll out a marketing campaign targeting mid‑market travel agencies within 60 days.</t>
+          <t>Partner with Vancouver’s tourism authority to create a curated travel package that highlights the new Car‑Free Granville Street experience, integrating real‑time pedestrian zone data into MONDEE’s itinerary builder; launch the campaign in Q3 to capture early adopters.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Capitalize on Vancouver’s new pedestrian zone by creating a localized travel package that includes exclusive access to Granville Street events, partnering with local businesses, and promoting it through MONDEE’s mobile app and social channels within 45 days to capture the growing urban tourism market.</t>
+          <t>Negotiate a white‑label integration with Priceline Partner Network to embed MONDEE’s unique experiences into their engine, expanding distribution while maintaining brand control; target a pilot with 3 major travel agencies by end of fiscal year.</t>
         </is>
       </c>
     </row>
@@ -2981,17 +2981,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Launch a back‑office API suite for travel advisors that mirrors Expedia TAAP’s new tools, enabling agencies to manage bookings, references, and reporting directly from MONDEE’s platform.</t>
+          <t>Launch a dedicated back‑office API suite for travel agencies, mirroring Expedia TAAP’s new tools, and roll out a 90‑day beta with key agency partners to gather feedback and iterate.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Introduce a tiered rewards program for agencies that book through MONDEE, matching or exceeding Expedia TAAP’s rewards to incentivize partner loyalty.</t>
+          <t>Introduce a tiered rewards program for travel advisors that integrates with MONDEE’s platform, offering points, discounts, and exclusive content, to match Expedia TAAP Rewards and drive higher engagement.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Partner with Priceline Partner Network to embed MONDEE’s AI‑driven itinerary optimization into their white‑label engine, creating a differentiated, value‑added offering that counters Expedia’s agency focus.</t>
+          <t>Build a white‑label travel engine that partners can embed into their own sites, replicating Priceline Partner Network’s model, and launch a pilot with 3 major travel agencies within the next 6 months.</t>
         </is>
       </c>
     </row>

--- a/News_Dashboard/data/raw_news_database_Mondee.xlsx
+++ b/News_Dashboard/data/raw_news_database_Mondee.xlsx
@@ -2846,17 +2846,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Develop a back‑office API and tools tailored for US travel advisors, mirroring Expedia TAAP, and launch a pilot with the top 10 agencies to secure early adoption.</t>
+          <t>Develop a US‑focused behind‑the‑scenes travel advisor engine that rivals Expedia TAAP, integrating AI itinerary optimization and real‑time pricing feeds; launch a pilot with 10 key advisors by Q3. This will position MONDEE as the preferred partner for travel agencies seeking advanced back‑office tools.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Create a white‑label travel engine for US brands, offering a revenue‑share model to compete with Priceline Partner Network’s white‑label solution, and target 5 major brands for beta testing.</t>
+          <t>Partner with US brands to deploy a white‑label travel engine similar to Priceline Partner Network, emphasizing sustainability metrics and local experience curation; secure at least three brand agreements by end of Q4.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Partner with Vancouver’s tourism board to build a digital guide and booking integration for the new car‑free Granville Street zone, positioning MONDEE as the preferred tech partner for the expanded pedestrian experience.</t>
+          <t>Create a Vancouver‑centric travel package that highlights the new pedestrian zone, offering guided tours, local vendor discounts, and a mobile app for real‑time navigation; launch the package in partnership with the city council by summer.</t>
         </is>
       </c>
     </row>
@@ -2900,17 +2900,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Launch a proprietary TAAP‑style platform for US travel advisors, integrating a back‑office API and tools to streamline booking workflows and position MONDEE as the go‑to advisor solution.</t>
+          <t>Develop a US‑centric travel advisor platform that replicates Expedia TAAP’s behind‑the‑scenes engine, including a back‑office API and real‑time booking tools. Pilot the platform with 10 leading travel agencies within 90 days to validate adoption.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Develop a white‑label travel engine that partners can embed in their own sites, mirroring Priceline Partner Network’s model, to expand MONDEE’s distribution and revenue streams.</t>
+          <t>Create a white‑label travel engine similar to Priceline Partner Network, offering customizable booking modules to travel agencies and partners, and secure at least 5 partnership agreements within 6 months.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Conduct a rapid market analysis of US travel advisor pain points revealed by Expedia’s TAAP rollout, then develop a targeted feature set (e.g., real‑time inventory, commission management) to outpace competitors in advisor adoption.</t>
+          <t>Analyze Expedia’s new back‑office API to identify unmet features for travel advisors, then release a complementary add‑on that addresses these gaps (e.g., advanced analytics or dynamic pricing) within 4 months.</t>
         </is>
       </c>
     </row>
@@ -2927,17 +2927,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Launch a dedicated back‑office API suite for travel advisors that mirrors Expedia TAAP’s new tools, enabling agencies to manage bookings, references, and reporting directly within MONDEE’s platform; begin beta testing with 5 key agency partners within 90 days. This will position MONDEE as a direct alternative to TAAP and retain agency loyalty.</t>
+          <t>Launch a dedicated back‑office API suite for travel advisors that mirrors Expedia TAAP’s new tools, enabling agencies to manage bookings, reference data, and operational workflows directly within MONDEE’s platform. This will position MONDEE as a one‑stop solution for agency efficiency and counter Expedia’s recent API push.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Partner with Vancouver’s tourism authority to create a curated travel package that highlights the new Car‑Free Granville Street experience, integrating real‑time pedestrian zone data into MONDEE’s itinerary builder; launch the campaign in Q3 to capture early adopters.</t>
+          <t>Collaborate with Vancouver’s tourism authority to develop a curated travel package that highlights the new car‑free Granville Street, offering exclusive itineraries and real‑time updates to travelers. This leverages the positive market shift toward pedestrian zones and differentiates MONDEE’s experiential offerings.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Negotiate a white‑label integration with Priceline Partner Network to embed MONDEE’s unique experiences into their engine, expanding distribution while maintaining brand control; target a pilot with 3 major travel agencies by end of fiscal year.</t>
+          <t>Introduce a white‑label travel engine similar to Priceline Partner Network, allowing partners to brand MONDEE’s booking infrastructure while accessing our data and APIs. This will attract partners seeking a customizable solution and expand MONDEE’s reach beyond direct consumer sales.</t>
         </is>
       </c>
     </row>
@@ -2981,17 +2981,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Launch a dedicated back‑office API suite for travel agencies, mirroring Expedia TAAP’s new tools, and roll out a 90‑day beta with key agency partners to gather feedback and iterate.</t>
+          <t>Develop and launch a back‑office API suite for travel advisors, including booking reference tools, inventory management, and automated invoicing, to match Expedia TAAP’s recent feature rollout and attract agency partners.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Introduce a tiered rewards program for travel advisors that integrates with MONDEE’s platform, offering points, discounts, and exclusive content, to match Expedia TAAP Rewards and drive higher engagement.</t>
+          <t>Introduce a tiered rewards program for advisors, offering commissions and benefits for high‑volume bookings, directly countering Expedia TAAP Rewards and boosting MONDEE’s advisor retention.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Build a white‑label travel engine that partners can embed into their own sites, replicating Priceline Partner Network’s model, and launch a pilot with 3 major travel agencies within the next 6 months.</t>
+          <t>Secure a white‑label partnership with a leading travel engine (e.g., Priceline Partner Network) to provide MONDEE with a scalable booking platform, enabling rapid market entry while preserving brand identity.</t>
         </is>
       </c>
     </row>

--- a/News_Dashboard/data/raw_news_database_Mondee.xlsx
+++ b/News_Dashboard/data/raw_news_database_Mondee.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U20"/>
+  <dimension ref="A1:U21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
@@ -2629,6 +2629,92 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Downtown Travel News</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/search?q=%22Downtown+Travel%22+when:1d&amp;hl=en-US&amp;gl=US&amp;ceid=US:en</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://www.mychesco.com/a/news/regional/doylestown-street-closures-could-disrupt-downtown-travel-for-months/</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2026-07-30 16:20:00</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Downtown Travel</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Downtown Travel (Brand)</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Doylestown Street Closures Could Disrupt Downtown Travel for Months - MyChesCo</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Alec Robson</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>DOYLESTOWN, PA — Drivers should prepare for months of daytime and overnight road closures in downtown Doylestown as PECO Energy begins utility construction affecting sections of State Street and Main Street.
+Crews will close and detour one section of roadway at a time to minimize disruptions.
+Closures on State Street will occur between:
+Closures on Main Street will occur between State Street and Court Street. Drivers will be directed to use State Street and Court Street.
+Local access will be maintained throughout construction. Drivers should plan extra time when traveling through downtown Doylestown because backups and delays are expected. Seek alternate routes whenever possible, especially during business hours.
+The construction schedule is weather dependent and may change if conditions are unfavorable.
+With work expected to continue through early December, motorists should anticipate changing traffic patterns as different sections of State Street and Main Street are closed throughout the project.
+Do not let downtown road closures catch you by surprise. Check the latest road restrictions, detours and traffic alerts at the MyChesCo Traffic Center before heading out: https://www.mychesco.com/traffic/
+Support the local news that supports Chester County. MyChesCo delivers reliable, fact-based reporting and essential community resources—free for everyone. If you value that, click here to become a patron today.</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>2026-07-30 18:03:41</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>DOYLESTOWN, PA — Drivers should prepare for months of daytime and overnight road closures in downtown Doylestown as PECO Energy begins utility construction affecting sections of State Street and Main Street. Crews will close and detour one section of roadway at a time to minimize disruptions.</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Tier 4 - Low</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:T20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/News_Dashboard/data/raw_news_database_Mondee.xlsx
+++ b/News_Dashboard/data/raw_news_database_Mondee.xlsx
@@ -2691,11 +2691,31 @@
           <t>2026-07-30 18:03:41</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Downtown Travel executed general industry news movement impacting Mondee market segment</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Standard market activity by Downtown Travel. No direct action required for Mondee.</t>
+        </is>
+      </c>
       <c r="Q21" t="inlineStr">
         <is>
           <t>DOYLESTOWN, PA — Drivers should prepare for months of daytime and overnight road closures in downtown Doylestown as PECO Energy begins utility construction affecting sections of State Street and Main Street. Crews will close and detour one section of roadway at a time to minimize disruptions.</t>
@@ -2707,11 +2727,16 @@
         </is>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
           <t>Tier 4 - Low</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Overview</t>
         </is>
       </c>
     </row>
@@ -2932,17 +2957,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Develop a US‑focused behind‑the‑scenes travel advisor engine that rivals Expedia TAAP, integrating AI itinerary optimization and real‑time pricing feeds; launch a pilot with 10 key advisors by Q3. This will position MONDEE as the preferred partner for travel agencies seeking advanced back‑office tools.</t>
+          <t>Market conditions are currently stable.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Partner with US brands to deploy a white‑label travel engine similar to Priceline Partner Network, emphasizing sustainability metrics and local experience curation; secure at least three brand agreements by end of Q4.</t>
+          <t>No high-priority competitor moves detected in this timeframe.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Create a Vancouver‑centric travel package that highlights the new pedestrian zone, offering guided tours, local vendor discounts, and a mobile app for real‑time navigation; launch the package in partnership with the city council by summer.</t>
+          <t>Continue tracking standard sector intelligence.</t>
         </is>
       </c>
     </row>
@@ -2986,17 +3011,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Develop a US‑centric travel advisor platform that replicates Expedia TAAP’s behind‑the‑scenes engine, including a back‑office API and real‑time booking tools. Pilot the platform with 10 leading travel agencies within 90 days to validate adoption.</t>
+          <t>No competitor product launches or API releases cataloged.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Create a white‑label travel engine similar to Priceline Partner Network, offering customizable booking modules to travel agencies and partners, and secure at least 5 partnership agreements within 6 months.</t>
+          <t>Digital feature velocity remains normal.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Analyze Expedia’s new back‑office API to identify unmet features for travel advisors, then release a complementary add‑on that addresses these gaps (e.g., advanced analytics or dynamic pricing) within 4 months.</t>
+          <t>Continue monitoring competitor release notes.</t>
         </is>
       </c>
     </row>
@@ -3013,17 +3038,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Launch a dedicated back‑office API suite for travel advisors that mirrors Expedia TAAP’s new tools, enabling agencies to manage bookings, reference data, and operational workflows directly within MONDEE’s platform. This will position MONDEE as a one‑stop solution for agency efficiency and counter Expedia’s recent API push.</t>
+          <t>Market conditions are currently stable.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Collaborate with Vancouver’s tourism authority to develop a curated travel package that highlights the new car‑free Granville Street, offering exclusive itineraries and real‑time updates to travelers. This leverages the positive market shift toward pedestrian zones and differentiates MONDEE’s experiential offerings.</t>
+          <t>No high-priority competitor moves detected in this timeframe.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Introduce a white‑label travel engine similar to Priceline Partner Network, allowing partners to brand MONDEE’s booking infrastructure while accessing our data and APIs. This will attract partners seeking a customizable solution and expand MONDEE’s reach beyond direct consumer sales.</t>
+          <t>Continue tracking standard sector intelligence.</t>
         </is>
       </c>
     </row>
@@ -3067,17 +3092,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Develop and launch a back‑office API suite for travel advisors, including booking reference tools, inventory management, and automated invoicing, to match Expedia TAAP’s recent feature rollout and attract agency partners.</t>
+          <t>No competitor product launches or API releases cataloged.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Introduce a tiered rewards program for advisors, offering commissions and benefits for high‑volume bookings, directly countering Expedia TAAP Rewards and boosting MONDEE’s advisor retention.</t>
+          <t>Digital feature velocity remains normal.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Secure a white‑label partnership with a leading travel engine (e.g., Priceline Partner Network) to provide MONDEE with a scalable booking platform, enabling rapid market entry while preserving brand identity.</t>
+          <t>Continue monitoring competitor release notes.</t>
         </is>
       </c>
     </row>
